--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2458-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2458-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D56495C-EEA1-4649-80ED-9336BA22CEA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{557D7C0E-5CD6-474F-AC21-FF0415D19B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{74A9A7A5-96F0-453D-994F-25102E7EC376}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{244BB03C-4540-498A-B9DE-458DA3062659}"/>
   </bookViews>
   <sheets>
     <sheet name="2458-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1457,23 +1457,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44EB4C57-421E-4AE8-9896-F2D612B70896}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{073B6B15-2E75-48B5-9C8B-2F8F52C658F1}">
   <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1501,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1531,7 +1531,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1627,7 +1627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2021</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2020</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2019</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2018</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2017</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2016</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2015</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2014</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2013</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2012</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2011</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2010</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2009</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2008</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2007</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2006</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2005</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2004</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2003</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2002</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2001</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2000</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>1999</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>1998</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
         <v>37</v>
       </c>
